--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-01-2026.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£19.95</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.13</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£37.10</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£890.00</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-cw4000-cavity-wall-boards?variant=42844829909229 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,110.00</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-thermaclass-cavity-wall-21?variant=44170644357357 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
